--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92561772133</v>
+        <v>46157.93070462468</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93070462468</v>
+        <v>46157.93152686248</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93152686248</v>
+        <v>46157.93393458122</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93393458122</v>
+        <v>46157.93707908267</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93707908267</v>
+        <v>46158.28210482914</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28210482914</v>
+        <v>46158.29665469115</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29665469115</v>
+        <v>46158.29804651551</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29804651551</v>
+        <v>46158.33381192983</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381192983</v>
+        <v>46158.36847729461</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36847729461</v>
+        <v>46158.37281415101</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
